--- a/templates/test_files/Strukturvorlage_DataDictionary_test1.xlsx
+++ b/templates/test_files/Strukturvorlage_DataDictionary_test1.xlsx
@@ -8,16 +8,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impressum" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary_core" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Header" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary_public" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objekte" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merkmale" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Werte" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dokumente" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merkmalgruppen" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Properties" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Values" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GroupOfProperties" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Template" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gelöschte Bauteile" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdownregeln" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <externalReferences>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
@@ -80,12 +80,12 @@
     <definedName name="GLO_Property7" localSheetId="1">Anleitung!$K$174</definedName>
     <definedName name="GLO_Property8" localSheetId="1">Anleitung!$K$175</definedName>
     <definedName name="GLO_Property9" localSheetId="1">Anleitung!$K$176</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Merkmale'!$A$2:$V$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Properties'!$A$2:$V$60</definedName>
     <definedName name="Objektkatalog_Start" localSheetId="6">[1]Wertekatalog!#REF!</definedName>
     <definedName name="DataTypes" localSheetId="7">[2]Dropdownregeln!#REF!</definedName>
     <definedName name="Units" localSheetId="7">[2]Dropdownregeln!#REF!</definedName>
     <definedName name="Merkmalskatalog_Start" localSheetId="8">'[3]MG Katalog'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Merkmalgruppen'!$A$2:$N$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GroupOfProperties'!$A$2:$N$60</definedName>
     <definedName name="DataTypes" localSheetId="9">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2581,12 +2581,12 @@
     <row r="1" ht="17.65" customHeight="1" s="228">
       <c r="C1" s="35" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GoP</t>
         </is>
       </c>
       <c r="E1" s="35" t="inlineStr">
         <is>
-          <t>Merkmale</t>
+          <t>Properties</t>
         </is>
       </c>
       <c r="F1" s="35" t="n"/>
@@ -2644,7 +2644,7 @@
       <c r="BF1" s="35" t="n"/>
       <c r="BI1" s="35" t="inlineStr">
         <is>
-          <t>Dokumente</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="BJ1" s="35" t="n"/>
@@ -2655,12 +2655,12 @@
     <row r="2" ht="163.5" customFormat="1" customHeight="1" s="189">
       <c r="C2" s="85" t="inlineStr">
         <is>
-          <t>Merkmalgruppe - Bezeichnung/Designation</t>
+          <t>GoP - Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
       <c r="E2" s="85" t="inlineStr">
         <is>
-          <t>Merkmal - Bezeichnung/Designation</t>
+          <t>Property - Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
       <c r="F2" s="58" t="inlineStr">
@@ -2722,7 +2722,7 @@
       <c r="BF2" s="190" t="n"/>
       <c r="BI2" s="85" t="inlineStr">
         <is>
-          <t>Dokumente - Bezeichnung/Designation</t>
+          <t>Document - Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
       <c r="BJ2" s="190" t="n"/>
@@ -2733,7 +2733,7 @@
     <row r="3" ht="17.25" customHeight="1" s="228">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Objekte</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="B3" s="84" t="n"/>
@@ -2795,7 +2795,7 @@
     <row r="4" ht="25.5" customFormat="1" customHeight="1" s="192">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Objekt - Bezeichnung/Designation</t>
+          <t>Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
       <c r="B4" s="204" t="n"/>
@@ -10595,7 +10595,11 @@
           <t>OrganizationCode</t>
         </is>
       </c>
-      <c r="B4" s="201" t="n"/>
+      <c r="B4" s="201" t="inlineStr">
+        <is>
+          <t>bDCH</t>
+        </is>
+      </c>
       <c r="C4" s="201" t="inlineStr">
         <is>
           <t>REQUIRED</t>
@@ -10613,7 +10617,11 @@
           <t>DictionaryCode</t>
         </is>
       </c>
-      <c r="B5" s="201" t="n"/>
+      <c r="B5" s="201" t="inlineStr">
+        <is>
+          <t>dd-fm</t>
+        </is>
+      </c>
       <c r="C5" s="201" t="inlineStr">
         <is>
           <t>REQUIRED</t>
@@ -10631,7 +10639,11 @@
           <t>DictionaryName (DE)</t>
         </is>
       </c>
-      <c r="B6" s="201" t="n"/>
+      <c r="B6" s="201" t="inlineStr">
+        <is>
+          <t>Datenkatalog Flächenmanagement</t>
+        </is>
+      </c>
       <c r="C6" s="201" t="inlineStr">
         <is>
           <t>REQUIRED</t>
@@ -10685,7 +10697,11 @@
           <t>DictionaryVersion</t>
         </is>
       </c>
-      <c r="B9" s="201" t="n"/>
+      <c r="B9" s="201" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
       <c r="C9" s="201" t="inlineStr">
         <is>
           <t>REQUIRED</t>
@@ -10703,7 +10719,11 @@
           <t>DictionaryUri</t>
         </is>
       </c>
-      <c r="B10" s="201" t="n"/>
+      <c r="B10" s="201" t="inlineStr">
+        <is>
+          <t>https://bauen-digital.ch/dictionary/dd-fm</t>
+        </is>
+      </c>
       <c r="C10" s="201" t="inlineStr">
         <is>
           <t>REQUIRED</t>
@@ -10745,7 +10765,11 @@
           <t>LifecycleStatus</t>
         </is>
       </c>
-      <c r="B13" s="201" t="n"/>
+      <c r="B13" s="201" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="C13" s="201" t="inlineStr">
         <is>
           <t>REQUIRED</t>
@@ -11558,27 +11582,27 @@
       </c>
       <c r="C1" s="135" t="inlineStr">
         <is>
-          <t>Strukturelle Einordnung</t>
+          <t>Structural categorisation</t>
         </is>
       </c>
       <c r="D1" s="100" t="inlineStr">
         <is>
-          <t>Domäne</t>
+          <t>Domain/Domäne/Domaine/Dominio</t>
         </is>
       </c>
       <c r="E1" s="100" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>System/System/Système/Sistema</t>
         </is>
       </c>
       <c r="F1" s="100" t="inlineStr">
         <is>
-          <t>Kategorie</t>
+          <t>Category/Kategorie/Catégorie/Categoria</t>
         </is>
       </c>
       <c r="G1" s="185" t="inlineStr">
         <is>
-          <t>Objekte</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="H1" s="100" t="inlineStr">
@@ -11588,12 +11612,12 @@
       </c>
       <c r="I1" s="100" t="inlineStr">
         <is>
-          <t>Objekt-ID</t>
+          <t>Class-ID</t>
         </is>
       </c>
       <c r="J1" s="100" t="inlineStr">
         <is>
-          <t>Objekt-Code</t>
+          <t>Class-Code</t>
         </is>
       </c>
       <c r="K1" s="100" t="inlineStr">
@@ -11648,7 +11672,7 @@
       </c>
       <c r="U1" s="100" t="inlineStr">
         <is>
-          <t>Objekte.IFC_URI</t>
+          <t>IFC_URI</t>
         </is>
       </c>
       <c r="V1" s="100" t="inlineStr">
@@ -11683,12 +11707,12 @@
       </c>
       <c r="AB1" s="100" t="inlineStr">
         <is>
-          <t>Versionsdatum</t>
+          <t>Version date</t>
         </is>
       </c>
       <c r="AC1" s="100" t="inlineStr">
         <is>
-          <t>Herkunft (PROV)</t>
+          <t>Provenance (PROV)</t>
         </is>
       </c>
       <c r="AD1" s="188" t="inlineStr">
@@ -12153,7 +12177,7 @@
       </c>
       <c r="AB7" s="123" t="inlineStr">
         <is>
-          <t>date format YYYY-MM-DD</t>
+          <t>date format 2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="AC7" s="123" t="inlineStr">
@@ -12177,7 +12201,11 @@
       <c r="F8" s="58" t="n"/>
       <c r="G8" s="136" t="n"/>
       <c r="H8" s="115" t="n"/>
-      <c r="I8" s="52" t="n"/>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>grundstueckflaeche</t>
+        </is>
+      </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
           <t>BdCH_Obj_81003201</t>
@@ -12246,7 +12274,7 @@
       </c>
       <c r="AB8" s="54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="AC8" s="54" t="inlineStr">
@@ -12890,7 +12918,7 @@
       </c>
       <c r="C1" s="112" t="inlineStr">
         <is>
-          <t>Merkmale</t>
+          <t>Properties</t>
         </is>
       </c>
       <c r="D1" s="122" t="inlineStr">
@@ -12900,12 +12928,12 @@
       </c>
       <c r="E1" s="197" t="inlineStr">
         <is>
-          <t>Merkmal-ID</t>
+          <t>Property-ID</t>
         </is>
       </c>
       <c r="F1" s="122" t="inlineStr">
         <is>
-          <t>Merkmal-Code</t>
+          <t>Property-Code</t>
         </is>
       </c>
       <c r="G1" s="122" t="inlineStr">
@@ -12983,7 +13011,7 @@
       </c>
       <c r="U1" s="100" t="inlineStr">
         <is>
-          <t>Einheit-Code</t>
+          <t>Units/Einheit/Unité/Unità</t>
         </is>
       </c>
       <c r="V1" s="100" t="inlineStr">
@@ -13013,7 +13041,7 @@
       </c>
       <c r="AA1" s="108" t="inlineStr">
         <is>
-          <t>Governance (Merkmale)</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="AB1" s="122" t="inlineStr">
@@ -13023,12 +13051,12 @@
       </c>
       <c r="AC1" s="122" t="inlineStr">
         <is>
-          <t>Versionsdatum</t>
+          <t>Version date</t>
         </is>
       </c>
       <c r="AD1" s="100" t="inlineStr">
         <is>
-          <t>Herkunft (PROV)</t>
+          <t>Provenance (PROV)</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13539,7 @@
       </c>
       <c r="AC7" s="123" t="inlineStr">
         <is>
-          <t>date format YYYY-MM-DD</t>
+          <t>date format 2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="AD7" s="220" t="inlineStr">
@@ -13524,8 +13552,16 @@
       <c r="A8" s="110" t="n"/>
       <c r="C8" s="110" t="n"/>
       <c r="D8" s="55" t="n"/>
-      <c r="E8" s="55" t="n"/>
-      <c r="F8" s="52" t="n"/>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>sia-380-2015-code</t>
+        </is>
+      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>SIA_380_2015_Code</t>
+        </is>
+      </c>
       <c r="G8" s="58" t="inlineStr">
         <is>
           <t>Raumbezeichnung</t>
@@ -13578,7 +13614,7 @@
       </c>
       <c r="AC8" s="54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="AD8" s="54" t="inlineStr">
@@ -17079,7 +17115,7 @@
       </c>
       <c r="C1" s="101" t="inlineStr">
         <is>
-          <t>Wertekatalog</t>
+          <t>Enumerations</t>
         </is>
       </c>
       <c r="D1" s="100" t="inlineStr">
@@ -17089,7 +17125,7 @@
       </c>
       <c r="E1" s="100" t="inlineStr">
         <is>
-          <t>Werteliste-ID</t>
+          <t>Enumeration-ID</t>
         </is>
       </c>
       <c r="F1" s="122" t="inlineStr">
@@ -17114,8 +17150,7 @@
       </c>
       <c r="J1" s="122" t="inlineStr">
         <is>
-          <t>EnumerationValues
-(EN)</t>
+          <t>Enumeration (EN)</t>
         </is>
       </c>
       <c r="K1" s="122" t="inlineStr">
@@ -17138,7 +17173,7 @@
       </c>
       <c r="N1" s="122" t="inlineStr">
         <is>
-          <t>Einheiten</t>
+          <t>Units/Einheit/Unité/Unità</t>
         </is>
       </c>
       <c r="O1" s="103" t="inlineStr">
@@ -17153,12 +17188,12 @@
       </c>
       <c r="Q1" s="100" t="inlineStr">
         <is>
-          <t>Versionsdatum</t>
+          <t>Version date</t>
         </is>
       </c>
       <c r="R1" s="100" t="inlineStr">
         <is>
-          <t>Quelle (PROV)</t>
+          <t>Provenance (PROV)</t>
         </is>
       </c>
     </row>
@@ -17433,7 +17468,7 @@
       </c>
       <c r="Q7" s="123" t="inlineStr">
         <is>
-          <t>date format YYYY-MM-DD</t>
+          <t>date format 2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="R7" s="220" t="inlineStr">
@@ -17447,7 +17482,11 @@
       <c r="B8" s="56" t="n"/>
       <c r="C8" s="49" t="n"/>
       <c r="D8" s="55" t="n"/>
-      <c r="E8" s="55" t="n"/>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>raumbezeichnung-sia-380_enum</t>
+        </is>
+      </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
           <t>Raumbezeichnung SIA 380</t>
@@ -17462,12 +17501,12 @@
       </c>
       <c r="J8" s="55" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>["1","2","3","4","5","6","7","8","9","10"]</t>
         </is>
       </c>
       <c r="K8" s="55" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>["1","2","3","4","5","6","7","8","9","10"]</t>
         </is>
       </c>
       <c r="L8" s="55" t="n"/>
@@ -17481,7 +17520,7 @@
       </c>
       <c r="Q8" s="54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="R8" s="54" t="inlineStr">
@@ -18482,7 +18521,7 @@
       </c>
       <c r="C1" s="212" t="inlineStr">
         <is>
-          <t>Dokumente</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="D1" s="212" t="inlineStr">
@@ -18543,7 +18582,7 @@
       <c r="O1" s="213" t="n"/>
       <c r="P1" s="212" t="inlineStr">
         <is>
-          <t>Governance (Dokumente)</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="Q1" s="212" t="inlineStr">
@@ -18553,12 +18592,12 @@
       </c>
       <c r="R1" s="212" t="inlineStr">
         <is>
-          <t>Versionsdatum</t>
+          <t>Version date</t>
         </is>
       </c>
       <c r="S1" s="212" t="inlineStr">
         <is>
-          <t>Herkunft (PROV)</t>
+          <t>Provenance (PROV)</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18889,7 @@
       </c>
       <c r="R7" s="222" t="inlineStr">
         <is>
-          <t>date format YYYY-MM-DD</t>
+          <t>date format 2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="S7" s="123" t="inlineStr">
@@ -18861,19 +18900,63 @@
     </row>
     <row r="8" ht="15" customFormat="1" customHeight="1" s="193">
       <c r="D8" s="92" t="n"/>
-      <c r="E8" s="207" t="n"/>
-      <c r="F8" s="207" t="n"/>
-      <c r="G8" s="207" t="n"/>
-      <c r="H8" s="207" t="n"/>
+      <c r="E8" s="207" t="inlineStr">
+        <is>
+          <t>organisation</t>
+        </is>
+      </c>
+      <c r="F8" s="207" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="G8" s="207" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="H8" s="207" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
       <c r="I8" s="207" t="n"/>
       <c r="J8" s="207" t="n"/>
-      <c r="K8" s="207" t="n"/>
-      <c r="L8" s="207" t="n"/>
-      <c r="M8" s="207" t="n"/>
-      <c r="N8" s="208" t="n"/>
-      <c r="Q8" s="54" t="n"/>
-      <c r="R8" s="54" t="n"/>
-      <c r="S8" s="54" t="n"/>
+      <c r="K8" s="207" t="inlineStr">
+        <is>
+          <t>intern</t>
+        </is>
+      </c>
+      <c r="L8" s="207" t="inlineStr">
+        <is>
+          <t>Zugänglich unentgeltlich</t>
+        </is>
+      </c>
+      <c r="M8" s="207" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="N8" s="208" t="inlineStr">
+        <is>
+          <t>bDCH</t>
+        </is>
+      </c>
+      <c r="Q8" s="54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R8" s="54" t="inlineStr">
+        <is>
+          <t>2026-06-18T15:30+02:00</t>
+        </is>
+      </c>
+      <c r="S8" s="54" t="inlineStr">
+        <is>
+          <t>bDCH</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="1" s="194">
       <c r="D9" s="92" t="n"/>
@@ -19553,17 +19636,17 @@
       </c>
       <c r="C1" s="211" t="inlineStr">
         <is>
-          <t>Merkmalgruppen</t>
+          <t>Group of Properties</t>
         </is>
       </c>
       <c r="D1" s="211" t="inlineStr">
         <is>
-          <t>Merkmalsgruppe-ID</t>
+          <t>GoP-ID</t>
         </is>
       </c>
       <c r="E1" s="211" t="inlineStr">
         <is>
-          <t>Merkmalsgruppe-Code</t>
+          <t>GoP-Code</t>
         </is>
       </c>
       <c r="F1" s="211" t="inlineStr">
@@ -19593,7 +19676,7 @@
       </c>
       <c r="K1" s="211" t="inlineStr">
         <is>
-          <t>Governance (Merkmalgruppen)</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="L1" s="211" t="inlineStr">
@@ -19603,12 +19686,12 @@
       </c>
       <c r="M1" s="211" t="inlineStr">
         <is>
-          <t>Versionsdatum</t>
+          <t>Version date</t>
         </is>
       </c>
       <c r="N1" s="211" t="inlineStr">
         <is>
-          <t>Herkunft (PROV)</t>
+          <t>Provenance (PROV)</t>
         </is>
       </c>
     </row>
@@ -19823,7 +19906,7 @@
       </c>
       <c r="M7" s="123" t="inlineStr">
         <is>
-          <t>date format YYYY-MM-DD</t>
+          <t>date format 2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="N7" s="220" t="inlineStr">
@@ -19839,11 +19922,19 @@
       <c r="E8" s="117" t="n"/>
       <c r="F8" s="53" t="inlineStr">
         <is>
-          <t>CH_AreaMgmt</t>
-        </is>
-      </c>
-      <c r="G8" s="54" t="n"/>
-      <c r="H8" s="117" t="n"/>
+          <t>bDCH_AreaMgmt</t>
+        </is>
+      </c>
+      <c r="G8" s="54" t="inlineStr">
+        <is>
+          <t>Area management property group</t>
+        </is>
+      </c>
+      <c r="H8" s="117" t="inlineStr">
+        <is>
+          <t>Merkmalsgruppe Flächenmanagement</t>
+        </is>
+      </c>
       <c r="I8" s="117" t="n"/>
       <c r="J8" s="117" t="n"/>
       <c r="K8" s="117" t="n"/>
@@ -19854,7 +19945,7 @@
       </c>
       <c r="M8" s="54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="N8" s="54" t="inlineStr">

--- a/templates/test_files/Strukturvorlage_DataDictionary_test1.xlsx
+++ b/templates/test_files/Strukturvorlage_DataDictionary_test1.xlsx
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B4" s="201" t="inlineStr">
         <is>
-          <t>bDCH</t>
+          <t>bdch</t>
         </is>
       </c>
       <c r="C4" s="201" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="B5" s="201" t="inlineStr">
         <is>
-          <t>dd-fm</t>
+          <t>datenkatalog_flaechenmanagement</t>
         </is>
       </c>
       <c r="C5" s="201" t="inlineStr">
@@ -10679,7 +10679,11 @@
           <t>DictionaryName (EN)</t>
         </is>
       </c>
-      <c r="B8" s="201" t="n"/>
+      <c r="B8" s="201" t="inlineStr">
+        <is>
+          <t>Data Dictionary Area Management</t>
+        </is>
+      </c>
       <c r="C8" s="201" t="inlineStr">
         <is>
           <t>OPTIONAL</t>
@@ -10721,7 +10725,7 @@
       </c>
       <c r="B10" s="201" t="inlineStr">
         <is>
-          <t>https://bauen-digital.ch/dictionary/dd-fm</t>
+          <t>https://example.com/bdch/datenkatalog_flaechenmanagement</t>
         </is>
       </c>
       <c r="C10" s="201" t="inlineStr">
@@ -11722,7 +11726,7 @@
       </c>
       <c r="AE1" s="100" t="inlineStr">
         <is>
-          <t>Objekte.RelatedDocument (Document-ID)</t>
+          <t>RelatedDocumentName (EN)</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12994,7 @@
       </c>
       <c r="Q1" s="122" t="inlineStr">
         <is>
-          <t>Werteliste-ID</t>
+          <t>EnumerationDesignation (EN)</t>
         </is>
       </c>
       <c r="R1" s="112" t="inlineStr">
@@ -13596,7 +13600,11 @@
           <t>IfcLabel</t>
         </is>
       </c>
-      <c r="Q8" s="55" t="n"/>
+      <c r="Q8" s="55" t="inlineStr">
+        <is>
+          <t>Raumbezeichnung SIA 380/2015</t>
+        </is>
+      </c>
       <c r="R8" s="110" t="n"/>
       <c r="S8" s="124" t="n"/>
       <c r="T8" s="53" t="n"/>
@@ -17496,7 +17504,7 @@
       <c r="H8" s="69" t="n"/>
       <c r="I8" s="69" t="inlineStr">
         <is>
-          <t>Raumbezeichnung SIA 380</t>
+          <t>Raumbezeichnung SIA 380/2015</t>
         </is>
       </c>
       <c r="J8" s="55" t="inlineStr">
@@ -18489,7 +18497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col width="5.5703125" bestFit="1" customWidth="1" style="36" min="1" max="1"/>
@@ -18526,7 +18534,7 @@
       </c>
       <c r="D1" s="212" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>GUID/URI</t>
         </is>
       </c>
       <c r="E1" s="212" t="inlineStr">
@@ -18561,12 +18569,12 @@
       </c>
       <c r="K1" s="212" t="inlineStr">
         <is>
-          <t>Sicherheitsstufe</t>
+          <t>Security level/Sicherheitsstufe/Niveau de sécurité/Livello di sicurezza</t>
         </is>
       </c>
       <c r="L1" s="212" t="inlineStr">
         <is>
-          <t>Zugänglichkeit</t>
+          <t>Accessibility/Zugänglichkeit/Accessibilité/Accessibilità</t>
         </is>
       </c>
       <c r="M1" s="212" t="inlineStr">
@@ -18579,23 +18587,22 @@
           <t>DocumentOwner</t>
         </is>
       </c>
-      <c r="O1" s="213" t="n"/>
+      <c r="O1" s="212" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
       <c r="P1" s="212" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="Q1" s="212" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Version date</t>
         </is>
       </c>
       <c r="R1" s="212" t="inlineStr">
-        <is>
-          <t>Version date</t>
-        </is>
-      </c>
-      <c r="S1" s="212" t="inlineStr">
         <is>
           <t>Provenance (PROV)</t>
         </is>
@@ -18620,10 +18627,9 @@
       <c r="L2" s="66" t="n"/>
       <c r="M2" s="66" t="n"/>
       <c r="N2" s="66" t="n"/>
-      <c r="O2" s="49" t="n"/>
-      <c r="Q2" s="67" t="n"/>
-      <c r="R2" s="66" t="n"/>
-      <c r="S2" s="67" t="n"/>
+      <c r="P2" s="67" t="n"/>
+      <c r="Q2" s="66" t="n"/>
+      <c r="R2" s="67" t="n"/>
     </row>
     <row r="3" ht="15" customFormat="1" customHeight="1" s="99">
       <c r="A3" s="49" t="n"/>
@@ -18644,10 +18650,9 @@
       <c r="L3" s="66" t="n"/>
       <c r="M3" s="66" t="n"/>
       <c r="N3" s="66" t="n"/>
-      <c r="O3" s="49" t="n"/>
-      <c r="Q3" s="67" t="n"/>
-      <c r="R3" s="66" t="n"/>
-      <c r="S3" s="67" t="n"/>
+      <c r="P3" s="67" t="n"/>
+      <c r="Q3" s="66" t="n"/>
+      <c r="R3" s="67" t="n"/>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="30">
       <c r="A4" s="49" t="n"/>
@@ -18712,18 +18717,17 @@
           <t>multilingual</t>
         </is>
       </c>
-      <c r="O4" s="49" t="n"/>
+      <c r="P4" s="66" t="inlineStr">
+        <is>
+          <t>multilingual</t>
+        </is>
+      </c>
       <c r="Q4" s="66" t="inlineStr">
         <is>
           <t>multilingual</t>
         </is>
       </c>
       <c r="R4" s="66" t="inlineStr">
-        <is>
-          <t>multilingual</t>
-        </is>
-      </c>
-      <c r="S4" s="66" t="inlineStr">
         <is>
           <t>multilingual</t>
         </is>
@@ -18764,18 +18768,17 @@
           <t>referenced</t>
         </is>
       </c>
-      <c r="O5" s="49" t="n"/>
+      <c r="P5" s="66" t="inlineStr">
+        <is>
+          <t>referenced</t>
+        </is>
+      </c>
       <c r="Q5" s="66" t="inlineStr">
         <is>
           <t>referenced</t>
         </is>
       </c>
       <c r="R5" s="66" t="inlineStr">
-        <is>
-          <t>referenced</t>
-        </is>
-      </c>
-      <c r="S5" s="66" t="inlineStr">
         <is>
           <t>referenced</t>
         </is>
@@ -18808,14 +18811,13 @@
       </c>
       <c r="M6" s="66" t="n"/>
       <c r="N6" s="66" t="n"/>
-      <c r="O6" s="49" t="n"/>
-      <c r="Q6" s="67" t="inlineStr">
+      <c r="P6" s="67" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="R6" s="120" t="n"/>
-      <c r="S6" s="67" t="n"/>
+      <c r="Q6" s="120" t="n"/>
+      <c r="R6" s="67" t="n"/>
     </row>
     <row r="7" ht="56.25" customFormat="1" customHeight="1" s="196">
       <c r="A7" s="221" t="n"/>
@@ -18880,19 +18882,18 @@
           <t>user defined</t>
         </is>
       </c>
-      <c r="O7" s="221" t="n"/>
-      <c r="P7" s="80" t="n"/>
-      <c r="Q7" s="123" t="inlineStr">
+      <c r="O7" s="80" t="n"/>
+      <c r="P7" s="123" t="inlineStr">
         <is>
           <t>must match Dropdownregeln.Status</t>
         </is>
       </c>
-      <c r="R7" s="222" t="inlineStr">
+      <c r="Q7" s="222" t="inlineStr">
         <is>
           <t>date format 2026-06-18T15:30+02:00</t>
         </is>
       </c>
-      <c r="S7" s="123" t="inlineStr">
+      <c r="R7" s="123" t="inlineStr">
         <is>
           <t>user defined</t>
         </is>
@@ -18939,22 +18940,22 @@
       </c>
       <c r="N8" s="208" t="inlineStr">
         <is>
-          <t>bDCH</t>
+          <t>bdch</t>
+        </is>
+      </c>
+      <c r="P8" s="54" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="Q8" s="54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>2026-06-18T15:30+02:00</t>
         </is>
       </c>
       <c r="R8" s="54" t="inlineStr">
         <is>
-          <t>2026-06-18T15:30+02:00</t>
-        </is>
-      </c>
-      <c r="S8" s="54" t="inlineStr">
-        <is>
-          <t>bDCH</t>
+          <t>bdch</t>
         </is>
       </c>
     </row>
@@ -18970,10 +18971,10 @@
       <c r="L9" s="42" t="n"/>
       <c r="M9" s="39" t="n"/>
       <c r="N9" s="210" t="n"/>
-      <c r="P9" s="110" t="n"/>
+      <c r="O9" s="110" t="n"/>
+      <c r="P9" s="54" t="n"/>
       <c r="Q9" s="54" t="n"/>
       <c r="R9" s="54" t="n"/>
-      <c r="S9" s="54" t="n"/>
     </row>
     <row r="10" customFormat="1" s="32">
       <c r="D10" s="92" t="n"/>
@@ -18987,10 +18988,10 @@
       <c r="L10" s="42" t="n"/>
       <c r="M10" s="39" t="n"/>
       <c r="N10" s="210" t="n"/>
-      <c r="P10" s="110" t="n"/>
+      <c r="O10" s="110" t="n"/>
+      <c r="P10" s="54" t="n"/>
       <c r="Q10" s="54" t="n"/>
       <c r="R10" s="54" t="n"/>
-      <c r="S10" s="54" t="n"/>
     </row>
     <row r="11" customFormat="1" s="32">
       <c r="D11" s="92" t="n"/>
@@ -19004,10 +19005,10 @@
       <c r="L11" s="42" t="n"/>
       <c r="M11" s="39" t="n"/>
       <c r="N11" s="210" t="n"/>
-      <c r="P11" s="110" t="n"/>
+      <c r="O11" s="110" t="n"/>
+      <c r="P11" s="54" t="n"/>
       <c r="Q11" s="54" t="n"/>
       <c r="R11" s="54" t="n"/>
-      <c r="S11" s="54" t="n"/>
     </row>
     <row r="12" customFormat="1" s="32">
       <c r="D12" s="92" t="n"/>
@@ -19021,10 +19022,10 @@
       <c r="L12" s="42" t="n"/>
       <c r="M12" s="39" t="n"/>
       <c r="N12" s="210" t="n"/>
-      <c r="P12" s="110" t="n"/>
+      <c r="O12" s="110" t="n"/>
+      <c r="P12" s="54" t="n"/>
       <c r="Q12" s="54" t="n"/>
       <c r="R12" s="54" t="n"/>
-      <c r="S12" s="54" t="n"/>
     </row>
     <row r="13" customFormat="1" s="32">
       <c r="D13" s="92" t="n"/>
@@ -19038,10 +19039,10 @@
       <c r="L13" s="42" t="n"/>
       <c r="M13" s="39" t="n"/>
       <c r="N13" s="210" t="n"/>
-      <c r="P13" s="110" t="n"/>
+      <c r="O13" s="110" t="n"/>
+      <c r="P13" s="54" t="n"/>
       <c r="Q13" s="54" t="n"/>
       <c r="R13" s="54" t="n"/>
-      <c r="S13" s="54" t="n"/>
     </row>
     <row r="14" customFormat="1" s="32">
       <c r="D14" s="92" t="n"/>
@@ -19055,10 +19056,10 @@
       <c r="L14" s="42" t="n"/>
       <c r="M14" s="39" t="n"/>
       <c r="N14" s="210" t="n"/>
-      <c r="P14" s="110" t="n"/>
+      <c r="O14" s="110" t="n"/>
+      <c r="P14" s="54" t="n"/>
       <c r="Q14" s="54" t="n"/>
       <c r="R14" s="54" t="n"/>
-      <c r="S14" s="54" t="n"/>
     </row>
     <row r="15" customFormat="1" s="32">
       <c r="D15" s="92" t="n"/>
@@ -19072,10 +19073,10 @@
       <c r="L15" s="42" t="n"/>
       <c r="M15" s="39" t="n"/>
       <c r="N15" s="210" t="n"/>
-      <c r="P15" s="110" t="n"/>
+      <c r="O15" s="110" t="n"/>
+      <c r="P15" s="54" t="n"/>
       <c r="Q15" s="54" t="n"/>
       <c r="R15" s="54" t="n"/>
-      <c r="S15" s="54" t="n"/>
     </row>
     <row r="16" ht="15" customFormat="1" customHeight="1" s="193">
       <c r="D16" s="92" t="n"/>
@@ -19089,9 +19090,9 @@
       <c r="L16" s="207" t="n"/>
       <c r="M16" s="207" t="n"/>
       <c r="N16" s="208" t="n"/>
+      <c r="P16" s="54" t="n"/>
       <c r="Q16" s="54" t="n"/>
       <c r="R16" s="54" t="n"/>
-      <c r="S16" s="54" t="n"/>
     </row>
     <row r="17" customFormat="1" s="194">
       <c r="D17" s="92" t="n"/>
@@ -19105,10 +19106,10 @@
       <c r="L17" s="42" t="n"/>
       <c r="M17" s="39" t="n"/>
       <c r="N17" s="210" t="n"/>
-      <c r="P17" s="110" t="n"/>
+      <c r="O17" s="110" t="n"/>
+      <c r="P17" s="54" t="n"/>
       <c r="Q17" s="54" t="n"/>
       <c r="R17" s="54" t="n"/>
-      <c r="S17" s="54" t="n"/>
     </row>
     <row r="18" customFormat="1" s="32">
       <c r="D18" s="92" t="n"/>
@@ -19122,10 +19123,10 @@
       <c r="L18" s="42" t="n"/>
       <c r="M18" s="39" t="n"/>
       <c r="N18" s="210" t="n"/>
-      <c r="P18" s="110" t="n"/>
+      <c r="O18" s="110" t="n"/>
+      <c r="P18" s="54" t="n"/>
       <c r="Q18" s="54" t="n"/>
       <c r="R18" s="54" t="n"/>
-      <c r="S18" s="54" t="n"/>
     </row>
     <row r="19" customFormat="1" s="32">
       <c r="D19" s="92" t="n"/>
@@ -19139,10 +19140,10 @@
       <c r="L19" s="42" t="n"/>
       <c r="M19" s="39" t="n"/>
       <c r="N19" s="210" t="n"/>
-      <c r="P19" s="110" t="n"/>
+      <c r="O19" s="110" t="n"/>
+      <c r="P19" s="54" t="n"/>
       <c r="Q19" s="54" t="n"/>
       <c r="R19" s="54" t="n"/>
-      <c r="S19" s="54" t="n"/>
     </row>
     <row r="20" customFormat="1" s="32">
       <c r="D20" s="92" t="n"/>
@@ -19156,10 +19157,10 @@
       <c r="L20" s="42" t="n"/>
       <c r="M20" s="39" t="n"/>
       <c r="N20" s="210" t="n"/>
-      <c r="P20" s="110" t="n"/>
+      <c r="O20" s="110" t="n"/>
+      <c r="P20" s="54" t="n"/>
       <c r="Q20" s="54" t="n"/>
       <c r="R20" s="54" t="n"/>
-      <c r="S20" s="54" t="n"/>
     </row>
     <row r="21" customFormat="1" s="32">
       <c r="D21" s="92" t="n"/>
@@ -19173,10 +19174,10 @@
       <c r="L21" s="42" t="n"/>
       <c r="M21" s="39" t="n"/>
       <c r="N21" s="210" t="n"/>
-      <c r="P21" s="110" t="n"/>
+      <c r="O21" s="110" t="n"/>
+      <c r="P21" s="54" t="n"/>
       <c r="Q21" s="54" t="n"/>
       <c r="R21" s="54" t="n"/>
-      <c r="S21" s="54" t="n"/>
     </row>
     <row r="22" customFormat="1" s="32">
       <c r="D22" s="92" t="n"/>
@@ -19190,10 +19191,10 @@
       <c r="L22" s="42" t="n"/>
       <c r="M22" s="39" t="n"/>
       <c r="N22" s="210" t="n"/>
-      <c r="P22" s="110" t="n"/>
+      <c r="O22" s="110" t="n"/>
+      <c r="P22" s="54" t="n"/>
       <c r="Q22" s="54" t="n"/>
       <c r="R22" s="54" t="n"/>
-      <c r="S22" s="54" t="n"/>
     </row>
     <row r="23" customFormat="1" s="32">
       <c r="D23" s="92" t="n"/>
@@ -19207,10 +19208,10 @@
       <c r="L23" s="42" t="n"/>
       <c r="M23" s="39" t="n"/>
       <c r="N23" s="210" t="n"/>
-      <c r="P23" s="110" t="n"/>
+      <c r="O23" s="110" t="n"/>
+      <c r="P23" s="54" t="n"/>
       <c r="Q23" s="54" t="n"/>
       <c r="R23" s="54" t="n"/>
-      <c r="S23" s="54" t="n"/>
     </row>
     <row r="24" ht="15" customFormat="1" customHeight="1" s="193">
       <c r="D24" s="92" t="n"/>
@@ -19224,9 +19225,9 @@
       <c r="L24" s="207" t="n"/>
       <c r="M24" s="207" t="n"/>
       <c r="N24" s="208" t="n"/>
+      <c r="P24" s="54" t="n"/>
       <c r="Q24" s="54" t="n"/>
       <c r="R24" s="54" t="n"/>
-      <c r="S24" s="54" t="n"/>
     </row>
     <row r="25" customFormat="1" s="194">
       <c r="D25" s="92" t="n"/>
@@ -19240,10 +19241,10 @@
       <c r="L25" s="42" t="n"/>
       <c r="M25" s="39" t="n"/>
       <c r="N25" s="210" t="n"/>
-      <c r="P25" s="110" t="n"/>
+      <c r="O25" s="110" t="n"/>
+      <c r="P25" s="54" t="n"/>
       <c r="Q25" s="54" t="n"/>
       <c r="R25" s="54" t="n"/>
-      <c r="S25" s="54" t="n"/>
     </row>
     <row r="26" customFormat="1" s="32">
       <c r="D26" s="92" t="n"/>
@@ -19257,10 +19258,10 @@
       <c r="L26" s="42" t="n"/>
       <c r="M26" s="39" t="n"/>
       <c r="N26" s="210" t="n"/>
-      <c r="P26" s="110" t="n"/>
+      <c r="O26" s="110" t="n"/>
+      <c r="P26" s="54" t="n"/>
       <c r="Q26" s="54" t="n"/>
       <c r="R26" s="54" t="n"/>
-      <c r="S26" s="54" t="n"/>
     </row>
     <row r="27" customFormat="1" s="32">
       <c r="D27" s="92" t="n"/>
@@ -19274,10 +19275,10 @@
       <c r="L27" s="42" t="n"/>
       <c r="M27" s="39" t="n"/>
       <c r="N27" s="210" t="n"/>
-      <c r="P27" s="110" t="n"/>
+      <c r="O27" s="110" t="n"/>
+      <c r="P27" s="54" t="n"/>
       <c r="Q27" s="54" t="n"/>
       <c r="R27" s="54" t="n"/>
-      <c r="S27" s="54" t="n"/>
     </row>
     <row r="28" customFormat="1" s="32">
       <c r="D28" s="92" t="n"/>
@@ -19291,10 +19292,10 @@
       <c r="L28" s="42" t="n"/>
       <c r="M28" s="39" t="n"/>
       <c r="N28" s="210" t="n"/>
-      <c r="P28" s="110" t="n"/>
+      <c r="O28" s="110" t="n"/>
+      <c r="P28" s="54" t="n"/>
       <c r="Q28" s="54" t="n"/>
       <c r="R28" s="54" t="n"/>
-      <c r="S28" s="54" t="n"/>
     </row>
     <row r="29" customFormat="1" s="32">
       <c r="D29" s="92" t="n"/>
@@ -19308,10 +19309,10 @@
       <c r="L29" s="42" t="n"/>
       <c r="M29" s="39" t="n"/>
       <c r="N29" s="210" t="n"/>
-      <c r="P29" s="110" t="n"/>
+      <c r="O29" s="110" t="n"/>
+      <c r="P29" s="54" t="n"/>
       <c r="Q29" s="54" t="n"/>
       <c r="R29" s="54" t="n"/>
-      <c r="S29" s="54" t="n"/>
     </row>
     <row r="30" customFormat="1" s="32">
       <c r="D30" s="92" t="n"/>
@@ -19325,10 +19326,10 @@
       <c r="L30" s="42" t="n"/>
       <c r="M30" s="39" t="n"/>
       <c r="N30" s="210" t="n"/>
-      <c r="P30" s="110" t="n"/>
+      <c r="O30" s="110" t="n"/>
+      <c r="P30" s="54" t="n"/>
       <c r="Q30" s="54" t="n"/>
       <c r="R30" s="54" t="n"/>
-      <c r="S30" s="54" t="n"/>
     </row>
     <row r="31" customFormat="1" s="32">
       <c r="D31" s="92" t="n"/>
@@ -19342,235 +19343,235 @@
       <c r="L31" s="42" t="n"/>
       <c r="M31" s="39" t="n"/>
       <c r="N31" s="210" t="n"/>
-      <c r="P31" s="110" t="n"/>
+      <c r="O31" s="110" t="n"/>
+      <c r="P31" s="54" t="n"/>
       <c r="Q31" s="54" t="n"/>
       <c r="R31" s="54" t="n"/>
-      <c r="S31" s="54" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="228">
       <c r="H32" s="203" t="n"/>
       <c r="I32" s="203" t="n"/>
       <c r="J32" s="203" t="n"/>
-      <c r="P32" s="110" t="n"/>
+      <c r="O32" s="110" t="n"/>
+      <c r="P32" s="54" t="n"/>
       <c r="Q32" s="54" t="n"/>
       <c r="R32" s="54" t="n"/>
-      <c r="S32" s="54" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="228">
       <c r="H33" s="203" t="n"/>
       <c r="I33" s="203" t="n"/>
       <c r="J33" s="203" t="n"/>
-      <c r="P33" s="110" t="n"/>
+      <c r="O33" s="110" t="n"/>
+      <c r="P33" s="54" t="n"/>
       <c r="Q33" s="54" t="n"/>
       <c r="R33" s="54" t="n"/>
-      <c r="S33" s="54" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="228">
       <c r="H34" s="203" t="n"/>
       <c r="I34" s="203" t="n"/>
       <c r="J34" s="203" t="n"/>
-      <c r="P34" s="110" t="n"/>
+      <c r="O34" s="110" t="n"/>
+      <c r="P34" s="54" t="n"/>
       <c r="Q34" s="54" t="n"/>
       <c r="R34" s="54" t="n"/>
-      <c r="S34" s="54" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="228">
       <c r="H35" s="203" t="n"/>
       <c r="I35" s="203" t="n"/>
       <c r="J35" s="203" t="n"/>
-      <c r="P35" s="110" t="n"/>
+      <c r="O35" s="110" t="n"/>
+      <c r="P35" s="54" t="n"/>
       <c r="Q35" s="54" t="n"/>
       <c r="R35" s="54" t="n"/>
-      <c r="S35" s="54" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="228">
       <c r="H36" s="203" t="n"/>
       <c r="I36" s="203" t="n"/>
       <c r="J36" s="203" t="n"/>
-      <c r="P36" s="110" t="n"/>
+      <c r="O36" s="110" t="n"/>
+      <c r="P36" s="54" t="n"/>
       <c r="Q36" s="54" t="n"/>
       <c r="R36" s="54" t="n"/>
-      <c r="S36" s="54" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="228">
       <c r="H37" s="203" t="n"/>
       <c r="I37" s="203" t="n"/>
       <c r="J37" s="203" t="n"/>
-      <c r="P37" s="110" t="n"/>
+      <c r="O37" s="110" t="n"/>
+      <c r="P37" s="54" t="n"/>
       <c r="Q37" s="54" t="n"/>
       <c r="R37" s="54" t="n"/>
-      <c r="S37" s="54" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="228">
       <c r="H38" s="203" t="n"/>
       <c r="I38" s="203" t="n"/>
       <c r="J38" s="203" t="n"/>
-      <c r="P38" s="110" t="n"/>
+      <c r="O38" s="110" t="n"/>
+      <c r="P38" s="54" t="n"/>
       <c r="Q38" s="54" t="n"/>
       <c r="R38" s="54" t="n"/>
-      <c r="S38" s="54" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="228">
       <c r="H39" s="203" t="n"/>
       <c r="I39" s="203" t="n"/>
       <c r="J39" s="203" t="n"/>
-      <c r="P39" s="110" t="n"/>
+      <c r="O39" s="110" t="n"/>
+      <c r="P39" s="54" t="n"/>
       <c r="Q39" s="54" t="n"/>
       <c r="R39" s="54" t="n"/>
-      <c r="S39" s="54" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="228">
       <c r="H40" s="203" t="n"/>
       <c r="I40" s="203" t="n"/>
       <c r="J40" s="203" t="n"/>
-      <c r="P40" s="110" t="n"/>
+      <c r="O40" s="110" t="n"/>
+      <c r="P40" s="54" t="n"/>
       <c r="Q40" s="54" t="n"/>
       <c r="R40" s="54" t="n"/>
-      <c r="S40" s="54" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="228">
       <c r="H41" s="203" t="n"/>
       <c r="I41" s="203" t="n"/>
       <c r="J41" s="203" t="n"/>
-      <c r="P41" s="110" t="n"/>
+      <c r="O41" s="110" t="n"/>
+      <c r="P41" s="54" t="n"/>
       <c r="Q41" s="54" t="n"/>
       <c r="R41" s="54" t="n"/>
-      <c r="S41" s="54" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="228">
       <c r="H42" s="203" t="n"/>
       <c r="I42" s="203" t="n"/>
       <c r="J42" s="203" t="n"/>
-      <c r="P42" s="110" t="n"/>
+      <c r="O42" s="110" t="n"/>
+      <c r="P42" s="54" t="n"/>
       <c r="Q42" s="54" t="n"/>
       <c r="R42" s="54" t="n"/>
-      <c r="S42" s="54" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="228">
       <c r="H43" s="203" t="n"/>
       <c r="I43" s="203" t="n"/>
       <c r="J43" s="203" t="n"/>
-      <c r="P43" s="110" t="n"/>
+      <c r="O43" s="110" t="n"/>
+      <c r="P43" s="54" t="n"/>
       <c r="Q43" s="54" t="n"/>
       <c r="R43" s="54" t="n"/>
-      <c r="S43" s="54" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="228">
       <c r="H44" s="203" t="n"/>
       <c r="I44" s="203" t="n"/>
       <c r="J44" s="203" t="n"/>
-      <c r="P44" s="110" t="n"/>
+      <c r="O44" s="110" t="n"/>
+      <c r="P44" s="54" t="n"/>
       <c r="Q44" s="54" t="n"/>
       <c r="R44" s="54" t="n"/>
-      <c r="S44" s="54" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="228">
       <c r="H45" s="203" t="n"/>
       <c r="I45" s="203" t="n"/>
       <c r="J45" s="203" t="n"/>
-      <c r="P45" s="110" t="n"/>
+      <c r="O45" s="110" t="n"/>
+      <c r="P45" s="54" t="n"/>
       <c r="Q45" s="54" t="n"/>
       <c r="R45" s="54" t="n"/>
-      <c r="S45" s="54" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="228">
       <c r="H46" s="203" t="n"/>
       <c r="I46" s="203" t="n"/>
       <c r="J46" s="203" t="n"/>
-      <c r="P46" s="110" t="n"/>
+      <c r="O46" s="110" t="n"/>
+      <c r="P46" s="54" t="n"/>
       <c r="Q46" s="54" t="n"/>
       <c r="R46" s="54" t="n"/>
-      <c r="S46" s="54" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="228">
       <c r="H47" s="203" t="n"/>
       <c r="I47" s="203" t="n"/>
       <c r="J47" s="203" t="n"/>
-      <c r="P47" s="110" t="n"/>
+      <c r="O47" s="110" t="n"/>
+      <c r="P47" s="54" t="n"/>
       <c r="Q47" s="54" t="n"/>
       <c r="R47" s="54" t="n"/>
-      <c r="S47" s="54" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="228">
       <c r="H48" s="203" t="n"/>
       <c r="I48" s="203" t="n"/>
       <c r="J48" s="203" t="n"/>
-      <c r="P48" s="110" t="n"/>
+      <c r="O48" s="110" t="n"/>
+      <c r="P48" s="54" t="n"/>
       <c r="Q48" s="54" t="n"/>
       <c r="R48" s="54" t="n"/>
-      <c r="S48" s="54" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="228">
       <c r="H49" s="203" t="n"/>
       <c r="I49" s="203" t="n"/>
       <c r="J49" s="203" t="n"/>
-      <c r="P49" s="110" t="n"/>
+      <c r="O49" s="110" t="n"/>
+      <c r="P49" s="54" t="n"/>
       <c r="Q49" s="54" t="n"/>
       <c r="R49" s="54" t="n"/>
-      <c r="S49" s="54" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="228">
       <c r="H50" s="203" t="n"/>
       <c r="I50" s="203" t="n"/>
       <c r="J50" s="203" t="n"/>
-      <c r="P50" s="110" t="n"/>
+      <c r="O50" s="110" t="n"/>
+      <c r="P50" s="54" t="n"/>
       <c r="Q50" s="54" t="n"/>
       <c r="R50" s="54" t="n"/>
-      <c r="S50" s="54" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="228">
       <c r="H51" s="203" t="n"/>
       <c r="I51" s="203" t="n"/>
       <c r="J51" s="203" t="n"/>
-      <c r="P51" s="110" t="n"/>
+      <c r="O51" s="110" t="n"/>
+      <c r="P51" s="54" t="n"/>
       <c r="Q51" s="54" t="n"/>
       <c r="R51" s="54" t="n"/>
-      <c r="S51" s="54" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="228">
       <c r="H52" s="203" t="n"/>
       <c r="I52" s="203" t="n"/>
       <c r="J52" s="203" t="n"/>
-      <c r="P52" s="110" t="n"/>
+      <c r="O52" s="110" t="n"/>
+      <c r="P52" s="54" t="n"/>
       <c r="Q52" s="54" t="n"/>
       <c r="R52" s="54" t="n"/>
-      <c r="S52" s="54" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="228">
       <c r="H53" s="203" t="n"/>
       <c r="I53" s="203" t="n"/>
       <c r="J53" s="203" t="n"/>
-      <c r="P53" s="110" t="n"/>
+      <c r="O53" s="110" t="n"/>
+      <c r="P53" s="54" t="n"/>
       <c r="Q53" s="54" t="n"/>
       <c r="R53" s="54" t="n"/>
-      <c r="S53" s="54" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="228">
       <c r="H54" s="203" t="n"/>
       <c r="I54" s="203" t="n"/>
       <c r="J54" s="203" t="n"/>
-      <c r="P54" s="110" t="n"/>
+      <c r="O54" s="110" t="n"/>
+      <c r="P54" s="54" t="n"/>
       <c r="Q54" s="54" t="n"/>
       <c r="R54" s="54" t="n"/>
-      <c r="S54" s="54" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="228">
       <c r="H55" s="203" t="n"/>
       <c r="I55" s="203" t="n"/>
       <c r="J55" s="203" t="n"/>
-      <c r="P55" s="110" t="n"/>
+      <c r="O55" s="110" t="n"/>
+      <c r="P55" s="54" t="n"/>
       <c r="Q55" s="54" t="n"/>
       <c r="R55" s="54" t="n"/>
-      <c r="S55" s="54" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="228">
       <c r="H56" s="203" t="n"/>
       <c r="I56" s="203" t="n"/>
       <c r="J56" s="203" t="n"/>
-      <c r="P56" s="110" t="n"/>
+      <c r="O56" s="110" t="n"/>
+      <c r="P56" s="54" t="n"/>
       <c r="Q56" s="54" t="n"/>
       <c r="R56" s="54" t="n"/>
-      <c r="S56" s="54" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="4">
